--- a/artfynd/A 5500-2024 artfynd.xlsx
+++ b/artfynd/A 5500-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122753452</v>
       </c>
       <c r="B2" t="n">
-        <v>78499</v>
+        <v>78503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5500-2024 artfynd.xlsx
+++ b/artfynd/A 5500-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122753452</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
+        <v>78506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5500-2024 artfynd.xlsx
+++ b/artfynd/A 5500-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122753452</v>
       </c>
       <c r="B2" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5500-2024 artfynd.xlsx
+++ b/artfynd/A 5500-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122753452</v>
+        <v>113679974</v>
       </c>
       <c r="B2" t="n">
-        <v>78508</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Säljan NV, Hls</t>
+          <t>Gårdberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572432</v>
+        <v>572510</v>
       </c>
       <c r="R2" t="n">
-        <v>6863888</v>
+        <v>6863995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +758,11 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -775,7 +775,320 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113679972</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gårdberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>572497</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6863986</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113678737</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>tjärnen, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>572677</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6864164</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122753452</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Säljan NV, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>572432</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6863888</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
